--- a/小野町_引継ぎ_整理済/22_図表管理/小野町_第10期計画_図表データ管理台帳_20260929.xlsx
+++ b/小野町_引継ぎ_整理済/22_図表管理/小野町_第10期計画_図表データ管理台帳_20260929.xlsx
@@ -22,7 +22,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_f07_riyou" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_f08_hokenryo" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_f09_zaisei" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_自己点検" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_f21_jinko" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_f23_kubun" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_f31_jinzai" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_f32_keido" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_f33_chosa" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_f41_kofukin_moku" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_f43_torikaeshi" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_f44_kofukin_tatsu" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_f45_kofukin_bunpu" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_自己点検" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -140,10 +149,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -273,6 +282,1062 @@
           <val>
             <numRef>
               <f>'D_f01_nintei_suii'!$B$5:$B$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>総人口と高齢化率の推移・推計</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'D_f21_jinko'!B4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'D_f21_jinko'!$A$5:$A$11</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_f21_jinko'!$B$5:$B$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'D_f21_jinko'!C4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'D_f21_jinko'!$A$5:$A$11</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_f21_jinko'!$C$5:$C$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>区分別の給付費の見込み</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'D_f23_kubun'!B4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'D_f23_kubun'!$A$5:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_f23_kubun'!$B$5:$B$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'D_f23_kubun'!C4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'D_f23_kubun'!$A$5:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_f23_kubun'!$C$5:$C$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'D_f23_kubun'!D4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'D_f23_kubun'!$A$5:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_f23_kubun'!$D$5:$D$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>介護人材の需要と供給の見通し</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'D_f31_jinzai'!B4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'D_f31_jinzai'!$A$5:$A$11</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_f31_jinzai'!$B$5:$B$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'D_f31_jinzai'!C4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'D_f31_jinzai'!$A$5:$A$11</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_f31_jinzai'!$C$5:$C$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>調整済み軽度認定率</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'D_f32_keido'!B4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'D_f32_keido'!$A$5:$A$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_f32_keido'!$B$5:$B$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>総合事業の実施状況調査の回答</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'D_f33_chosa'!B4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'D_f33_chosa'!$A$5:$A$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_f33_chosa'!$B$5:$B$9</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'D_f33_chosa'!C4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'D_f33_chosa'!$A$5:$A$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_f33_chosa'!$C$5:$C$9</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'D_f33_chosa'!D4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'D_f33_chosa'!$A$5:$A$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_f33_chosa'!$D$5:$D$9</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'D_f33_chosa'!E4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'D_f33_chosa'!$A$5:$A$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_f33_chosa'!$E$5:$E$9</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>目標別の得点（小野町と全国平均）</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'D_f41_kofukin_moku'!B4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'D_f41_kofukin_moku'!$A$5:$A$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_f41_kofukin_moku'!$B$5:$B$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'D_f41_kofukin_moku'!C4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'D_f41_kofukin_moku'!$A$5:$A$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_f41_kofukin_moku'!$C$5:$C$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'D_f41_kofukin_moku'!D4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'D_f41_kofukin_moku'!$A$5:$A$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_f41_kofukin_moku'!$D$5:$D$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>全国平均に届いていない指標（伸びしろ）</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'D_f43_torikaeshi'!B4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'D_f43_torikaeshi'!$A$5:$A$14</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_f43_torikaeshi'!$B$5:$B$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'D_f43_torikaeshi'!C4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'D_f43_torikaeshi'!$A$5:$A$14</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_f43_torikaeshi'!$C$5:$C$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>指標群別の到達度</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'D_f44_kofukin_tatsu'!B4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'D_f44_kofukin_tatsu'!$A$5:$A$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_f44_kofukin_tatsu'!$B$5:$B$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'D_f44_kofukin_tatsu'!C4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'D_f44_kofukin_tatsu'!$A$5:$A$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_f44_kofukin_tatsu'!$C$5:$C$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart18.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>県内の得点の分布と小野町の位置</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'D_f45_kofukin_bunpu'!B4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'D_f45_kofukin_bunpu'!$A$5:$A$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_f45_kofukin_bunpu'!$B$5:$B$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'D_f45_kofukin_bunpu'!C4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'D_f45_kofukin_bunpu'!$A$5:$A$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_f45_kofukin_bunpu'!$C$5:$C$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'D_f45_kofukin_bunpu'!D4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'D_f45_kofukin_bunpu'!$A$5:$A$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_f45_kofukin_bunpu'!$D$5:$D$12</f>
             </numRef>
           </val>
         </ser>
@@ -1177,6 +2242,249 @@
 </wsDr>
 </file>
 
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -2508,248 +3816,511 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>99　自己点検</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>本表を作るたびに機械で確かめている項目。1件でも不適合があると生成は失敗で終わる。</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>図10　総人口と高齢化率の推移・推計</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>差し込み先：素案　第2章1　／　種類：折れ線・縦棒　／　出所：第10期将来推計用推計人口</t>
         </is>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>区分</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>確かめたこと</t>
+          <t>（系列）</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>期待</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>判定</t>
+          <t>（第2軸）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>図のPNGが実在する</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>19点すべて</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>19点</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>適合</t>
-        </is>
+          <t>令和5</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>9314</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>37.0303</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>図から数値を読み取れた</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>19点すべて</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>9点（読めず ['f21_jinko', 'f23_kubun', 'f31_jinzai', 'f32_keido', 'f33_chosa', 'f41_kofukin_moku', 'f42_kofukin_gun', 'f43_torikaeshi', 'f44_kofukin_tatsu', 'f45_kofukin_bunpu']）</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>不適合</t>
-        </is>
+          <t>令和6</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>9132</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>37.9435</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>成果品が実在する</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>9件すべて</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>9件</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>適合</t>
-        </is>
+          <t>令和7</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>8951</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>38.6549</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>成果品に差し込まれている図の延べ数</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>台帳の延べ 21点</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>成果品の中 20点</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>適合</t>
-        </is>
+          <t>令和8</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>8771</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>39.3228</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>認定者数の図の令和8年3月末が年報と合う</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>792人</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>792人</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>適合</t>
-        </is>
+          <t>令和9</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>8591</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>40.0186</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>図がない分析を04シートに掲げてある</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>4件すべて</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>04シートに 6件</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>適合</t>
-        </is>
+          <t>令和10</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>8411</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>40.7562</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>読み取った数値が空でない</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>空の図がない</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>空の図はない</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>適合</t>
-        </is>
+          <t>令和11</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>8232</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>41.5209</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>図11　区分別の給付費の見込み</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>差し込み先：素案　第6章2　／　種類：横棒・縦棒　／　出所：本業務による算定</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>居宅</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>施設</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>352.6902</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>318.448</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>349.9788</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>317.1092</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>347.2674</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>315.7705</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>図12　介護人材の需要と供給の見通し</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>差し込み先：総合事業ワークシートの確認結果　第3章　／　種類：折れ線・縦棒　／　出所：国の（改修版）総合事業の充実に向けたワークシート</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>認定者数の推計（需要）</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>生産年齢人口で縮めた供給可能量</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>2020年</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>788</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2025年</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>800</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>2030年</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>778</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>2035年</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>805</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>2040年</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>870</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>2045年</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>872</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>2050年</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>808</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>404</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>図13　調整済み軽度認定率</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>差し込み先：総合事業ワークシートの確認結果　第2章　／　種類：折れ線　／　出所：同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>小野町</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>平成29</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>12.22</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>平成30</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>12.82</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>令和元</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>13.02</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>令和2</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>14.12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>令和3</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>13.74</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>令和4</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>14.71</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>令和5</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>14.69</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>令和6</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>15.15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3249,14 +4820,14 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>折れ線・縦棒</t>
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
@@ -3292,14 +4863,14 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>横棒・縦棒</t>
         </is>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
@@ -3335,14 +4906,14 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>折れ線・縦棒</t>
         </is>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
@@ -3378,14 +4949,14 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>折れ線</t>
         </is>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
@@ -3421,14 +4992,14 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>縦棒</t>
         </is>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
@@ -3464,14 +5035,14 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>横棒</t>
         </is>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
@@ -3490,14 +5061,14 @@
           <t>f42_kofukin_gun</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>給付適正化と交付金の取りまとめ</t>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>（差し込み先なし）</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>第2章</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -3518,7 +5089,7 @@
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>令和8年度交付金 該当状況調査票集計表（市町村分）</t>
         </is>
       </c>
     </row>
@@ -3550,14 +5121,14 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>横棒</t>
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
@@ -3593,14 +5164,14 @@
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>横棒</t>
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
@@ -3636,18 +5207,1182 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>折れ線・縦棒</t>
         </is>
       </c>
       <c r="G23" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>図14　総合事業の実施状況調査の回答</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>差し込み先：総合事業ワークシートの確認結果　第4章　／　種類：縦棒　／　出所：同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>訪問型B 実人数</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>訪問型B 延べ人数</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>通所型B 実人数</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>通所型B 延べ人数</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>408</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>408</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>693</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>1051</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>921</v>
+      </c>
+      <c r="D8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="E8" s="6" t="n">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>図15　目標別の得点（小野町と全国平均）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>差し込み先：給付適正化と交付金の取りまとめ　第2章　／　種類：横棒　／　出所：令和8年度交付金 該当状況調査票集計表（市町村分）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>小野町</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>福島県平均</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>全国平均</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>63.2712</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>62.3691</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>70.77970000000001</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>69.10420000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>49.6949</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>50.0553</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>46.4407</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>47.7507</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>60.6102</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>57.9342</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>54.5085</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>51.5371</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>64.661</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>68.3398</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>46.4407</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>47.7507</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>図17　全国平均に届いていない指標（伸びしろ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>差し込み先：給付適正化と交付金の取りまとめ　第7章　／　種類：横棒　／　出所：同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>全国平均</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>小野町</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>11.2565</v>
+      </c>
+      <c r="C5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>同上</t>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>18.8704</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>18.416</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>6.7266</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>3.875</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>6.582</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>5.2865</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>1.9844</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>4.8145</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>4.8105</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>図18　指標群別の到達度</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>差し込み先：給付適正化と交付金の取りまとめ　第2章　／　種類：横棒　／　出所：同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>全国平均</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>小野町</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>81.8665</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>27.7072</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>33.3333</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>73.41070000000001</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>59.9528</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>66.276</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>81.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>21.2185</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>72.4409</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>92.3077</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>42.2187</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>60.4167</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>59.6985</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>76.5625</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>37.028</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>66.66670000000001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>81.4396</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>63.2353</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>40.5029</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>37.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>図19　県内の得点の分布と小野町の位置</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>差し込み先：給付適正化と交付金の取りまとめ　第3章　／　種類：折れ線・縦棒　／　出所：同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>（系列）</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>（系列）</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>（系列）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>99　自己点検</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>本表を作るたびに機械で確かめている項目。1件でも不適合があると生成は失敗で終わる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>確かめたこと</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>期待</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>図のPNGが実在する</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>19点すべて</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>19点</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>差し込んでいる図から数値を読み取れた</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>18点すべて</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>18点</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>定義はあるが差し込んでいない図</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>把握していること</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>1点（f42_kofukin_gun）</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>成果品が実在する</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>9件すべて</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>9件</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>成果品に差し込まれている図の延べ数</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>台帳の延べ 20点</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>成果品の中 20点</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>認定者数の図の令和8年3月末が年報と合う</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>792人</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>792人</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>図がない分析を04シートに掲げてある</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>4件すべて</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>04シートに 6件</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>読み取った数値が空でない</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>空の図がない</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>空の図はない</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>適合</t>
         </is>
       </c>
     </row>
@@ -3741,7 +6476,7 @@
       <c r="E5" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -3769,7 +6504,7 @@
       <c r="E6" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -3797,7 +6532,7 @@
       <c r="E7" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -3825,7 +6560,7 @@
       <c r="E8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -3853,7 +6588,7 @@
       <c r="E9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -3881,7 +6616,7 @@
       <c r="E10" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -3909,7 +6644,7 @@
       <c r="E11" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -3937,7 +6672,7 @@
       <c r="E12" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
@@ -3965,14 +6700,14 @@
       <c r="E13" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>計</t>
         </is>
@@ -4139,7 +6874,7 @@
           <t>ある</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>主要3事業の実施状況そのものを示す図はない</t>
         </is>
@@ -4189,7 +6924,7 @@
           <t>ない</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>要介護度の維持・改善率の図がない。見える化システムのB系列から作れる</t>
         </is>
@@ -4216,7 +6951,7 @@
           <t>ある</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>通いの場の参加率・箇所数の推移の図がない</t>
         </is>
@@ -4243,7 +6978,7 @@
           <t>ない</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>地域ケア会議の開催回数・検討件数の図がない。町の事業実績が要る</t>
         </is>
@@ -4270,7 +7005,7 @@
           <t>ない</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>入院時情報連携加算・退院・退所加算の算定者数割合の図がない。交付金の失点が最も大きい分野であり、優先して作る</t>
         </is>
@@ -4297,7 +7032,7 @@
           <t>ない</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>自立度Ⅱa以上の人数、推進員・カフェ・初期集中支援チームの実績の図がない</t>
         </is>
@@ -4371,12 +7106,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>入院時情報連携加算・退院・退所加算の算定者数割合</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>支援Ⅲの失点45点のうち活動指標群20点の説明。入院時は上位1割で満点、退院時は上位7割にも入っていない</t>
         </is>
@@ -4386,7 +7121,7 @@
           <t>令和8年度交付金 該当状況調査票集計表（受領済み）</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>最優先</t>
         </is>
@@ -4398,7 +7133,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>認知症施策の実績（自立度Ⅱa以上の人数、推進員、カフェ、初期集中支援チームの訪問実績）</t>
         </is>
@@ -4413,7 +7148,7 @@
           <t>見える化システム J系列（受領済み）</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -4425,7 +7160,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>通いの場の参加率・箇所数の推移</t>
         </is>
@@ -4435,12 +7170,12 @@
           <t>第3章1の評価（週1回以上が0か所）と第5章 基本目標1② の裏づけ</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>見える化システム F系列（受領済み）。町の事業実績との食い違いの確認が要る</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -4489,7 +7224,7 @@
           <t>支援Ⅱ(ⅰ)の説明、第5章 基本目標3① の成果指標</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>町の事業実績（未受領）</t>
         </is>
@@ -4516,7 +7251,7 @@
           <t>推進Ⅱ(ⅰ)の説明、給付適正化計画の目標の裏づけ</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>町の適正化事業の実施報告（未受領）</t>
         </is>
@@ -4596,7 +7331,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>図13／図14／図16／図17／図18／図19</t>
+          <t>図13／図14／図17／図18／図19</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr"/>
@@ -4622,7 +7357,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告（年報）様式1の5</t>
+          <t>令和8年度交付金 該当状況調査票集計表（市町村分）</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -4632,7 +7367,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>図1</t>
+          <t>図15／図16</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr"/>
@@ -4640,7 +7375,7 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>年報 様式1の5</t>
+          <t>介護保険事業状況報告（年報）様式1の5</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -4650,7 +7385,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>図2</t>
+          <t>図1</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr"/>
@@ -4658,7 +7393,7 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>年報 様式3</t>
+          <t>年報 様式1の5</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -4668,7 +7403,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>図3</t>
+          <t>図2</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr"/>
@@ -4676,7 +7411,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>第9期計画本文及び年報 様式3</t>
+          <t>年報 様式3</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -4686,7 +7421,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>図4</t>
+          <t>図3</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr"/>
@@ -4694,7 +7429,7 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>国保連合会業務統計表（月報）</t>
+          <t>第9期計画本文及び年報 様式3</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -4704,7 +7439,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>図5</t>
+          <t>図4</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr"/>
@@ -4712,7 +7447,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>見える化システム</t>
+          <t>国保連合会業務統計表（月報）</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -4722,7 +7457,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>図7</t>
+          <t>図5</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr"/>
@@ -4730,7 +7465,7 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>本業務による算定及び見える化システムの出力</t>
+          <t>見える化システム</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -4740,7 +7475,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>図8</t>
+          <t>図7</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr"/>
@@ -4748,7 +7483,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>第10期将来推計用推計人口</t>
+          <t>本業務による算定及び見える化システムの出力</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -4758,7 +7493,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>図10</t>
+          <t>図8</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr"/>
@@ -4766,7 +7501,7 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>本業務による算定</t>
+          <t>第10期将来推計用推計人口</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -4776,7 +7511,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>図11</t>
+          <t>図10</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr"/>
@@ -4784,7 +7519,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>国の（改修版）総合事業の充実に向けたワークシート</t>
+          <t>本業務による算定</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -4794,7 +7529,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>図12</t>
+          <t>図11</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr"/>
@@ -4802,7 +7537,7 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>令和8年度交付金 該当状況調査票集計表（市町村分）</t>
+          <t>国の（改修版）総合事業の充実に向けたワークシート</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -4812,7 +7547,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>図15</t>
+          <t>図12</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr"/>

--- a/小野町_引継ぎ_整理済/22_図表管理/小野町_第10期計画_図表データ管理台帳_20260929.xlsx
+++ b/小野町_引継ぎ_整理済/22_図表管理/小野町_第10期計画_図表データ管理台帳_20260929.xlsx
@@ -31,7 +31,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_f43_torikaeshi" sheetId="22" state="visible" r:id="rId22"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_f44_kofukin_tatsu" sheetId="23" state="visible" r:id="rId23"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_f45_kofukin_bunpu" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_自己点検" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_f46_nyutaiin" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_自己点検" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1377,6 +1378,112 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart19.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>入退院支援と人生の最終段階における支援の位置（活動指標群）</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'D_f46_nyutaiin'!B4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'D_f46_nyutaiin'!$A$5:$A$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_f46_nyutaiin'!$B$5:$B$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'D_f46_nyutaiin'!C4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'D_f46_nyutaiin'!$A$5:$A$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_f46_nyutaiin'!$C$5:$C$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
@@ -2485,6 +2592,33 @@
 </wsDr>
 </file>
 
+<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -4330,7 +4464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5217,6 +5351,49 @@
         <v>8</v>
       </c>
       <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>図20</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>f46_nyutaiin</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>給付適正化と交付金の取りまとめ</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>第5章(4)</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>入退院支援と人生の最終段階における支援の位置（活動指標群）</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>横棒</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -6119,6 +6296,109 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>図20　入退院支援と人生の最終段階における支援の位置（活動指標群）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>差し込み先：給付適正化と交付金の取りまとめ　第5章(4)　／　種類：横棒　／　出所：同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>（系列）</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>（系列）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6183,12 +6463,12 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>19点すべて</t>
+          <t>20点すべて</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>19点</t>
+          <t>20点</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -6210,12 +6490,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>18点すべて</t>
+          <t>19点すべて</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>18点</t>
+          <t>19点</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -6291,12 +6571,12 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>台帳の延べ 20点</t>
+          <t>台帳の延べ 21点</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>成果品の中 20点</t>
+          <t>成果品の中 21点</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -6642,7 +6922,7 @@
         <v>23</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
@@ -6718,7 +6998,7 @@
         <v>305</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F14" s="6" t="inlineStr"/>
     </row>
@@ -6733,7 +7013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6987,52 +7267,79 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>支援Ⅲ(ⅰ)(ⅱ)</t>
+          <t>支援Ⅲ(ⅱ)</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>在宅医療・在宅介護連携</t>
+          <t>在宅医療・在宅介護連携（活動指標群）</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>ない</t>
+          <t>f46_nyutaiin</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>ある</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>入院時情報連携加算・退院・退所加算の算定者数割合の図がない。交付金の失点が最も大きい分野であり、優先して作る</t>
+          <t>令和8年9月29日に作成。入院時情報連携加算は上位1割で配点満点、退院・退所加算は上位7割にも入らず0点。ターミナルケア・看取りは上位7割</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
+          <t>支援Ⅲ(ⅰ)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>在宅医療・在宅介護連携（体制・取組指標群）</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>ない</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>0点の5枝番（4つの場面ごとの目指すべき姿の設定ほか）を示す図がない。表では示している（第5章(2)）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
           <t>支援Ⅲ</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>認知症施策</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>ない</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>自立度Ⅱa以上の人数、推進員・カフェ・初期集中支援チームの実績の図がない</t>
         </is>
@@ -7101,9 +7408,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>済</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -7123,7 +7430,7 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>最優先</t>
+          <t>令和8年9月29日に作成（f46_nyutaiin）</t>
         </is>
       </c>
     </row>
@@ -7331,7 +7638,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>図13／図14／図17／図18／図19</t>
+          <t>図13／図14／図17／図18／図19／図20</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr"/>

--- a/小野町_引継ぎ_整理済/22_図表管理/小野町_第10期計画_図表データ管理台帳_20260929.xlsx
+++ b/小野町_引継ぎ_整理済/22_図表管理/小野町_第10期計画_図表データ管理台帳_20260929.xlsx
@@ -32,7 +32,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_f44_kofukin_tatsu" sheetId="23" state="visible" r:id="rId23"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_f45_kofukin_bunpu" sheetId="24" state="visible" r:id="rId24"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_f46_nyutaiin" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_自己点検" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_f47_ninchisho" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_自己点検" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1566,6 +1567,88 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart20.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>認知症施策の体制と活動</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'D_f47_ninchisho'!B4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'D_f47_ninchisho'!$A$5:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_f47_ninchisho'!$B$5:$B$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
@@ -2646,6 +2729,33 @@
 </wsDr>
 </file>
 
+<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -4464,7 +4574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5396,6 +5506,49 @@
       <c r="I24" s="6" t="inlineStr">
         <is>
           <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>図21</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>f47_ninchisho</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>計画素案・協議会資料</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>素案 第5章 基本目標2③／協議会資料 第1部4-3</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>認知症施策の体制と活動</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>縦棒</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>見える化システム J16・J17・J18（厚生労働省「認知症総合支援事業等実施状況調べ」）</t>
         </is>
       </c>
     </row>
@@ -6399,6 +6552,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>図21　認知症施策の体制と活動</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>差し込み先：計画素案・協議会資料　素案 第5章 基本目標2③／協議会資料 第1部4-3　／　種類：縦棒　／　出所：見える化システム J16・J17・J18（厚生労働省「認知症総合支援事業等実施状況調べ」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>（系列）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>令和3年3月</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>令和6年3月</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6463,12 +6681,12 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>20点すべて</t>
+          <t>21点すべて</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>20点</t>
+          <t>21点</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -6490,12 +6708,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>19点すべて</t>
+          <t>20点すべて</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>19点</t>
+          <t>20点</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -6571,12 +6789,12 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>台帳の延べ 21点</t>
+          <t>台帳の延べ 23点</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>成果品の中 21点</t>
+          <t>成果品の中 23点</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -6625,7 +6843,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>4件すべて</t>
+          <t>3件すべて</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -6754,7 +6972,7 @@
         <v>99</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
@@ -6782,7 +7000,7 @@
         <v>50</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
@@ -6998,7 +7216,7 @@
         <v>305</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F14" s="6" t="inlineStr"/>
     </row>
@@ -7321,27 +7539,27 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>支援Ⅲ</t>
+          <t>支援Ⅱ(ⅰ)</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>認知症施策</t>
+          <t>認知症総合支援</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>ない</t>
+          <t>f47_ninchisho</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>ある</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>自立度Ⅱa以上の人数、推進員・カフェ・初期集中支援チームの実績の図がない</t>
+          <t>令和8年10月1日に作成。推進員1→4人、カフェ1か所で横ばい、初期集中支援チームの訪問実績0件。自立度Ⅱa以上の人数は時点（平成24年→令和6年）が体制の指標（令和3年→令和6年）と違うため、同じ図に並べていない</t>
         </is>
       </c>
     </row>
@@ -7435,14 +7653,14 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>済</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>認知症施策の実績（自立度Ⅱa以上の人数、推進員、カフェ、初期集中支援チームの訪問実績）</t>
+          <t>認知症施策の実績（推進員、カフェ、初期集中支援チームの訪問実績）</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -7457,7 +7675,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>令和8年10月1日に作成（f47_ninchisho）</t>
         </is>
       </c>
     </row>
@@ -7580,7 +7798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -7858,6 +8076,24 @@
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>見える化システム J16・J17・J18（厚生労働省「認知症総合支援事業等実施状況調べ」）</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>受領済み</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>図21</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/小野町_引継ぎ_整理済/22_図表管理/小野町_第10期計画_図表データ管理台帳_20260929.xlsx
+++ b/小野町_引継ぎ_整理済/22_図表管理/小野町_第10期計画_図表データ管理台帳_20260929.xlsx
@@ -33,7 +33,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_f45_kofukin_bunpu" sheetId="24" state="visible" r:id="rId24"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_f46_nyutaiin" sheetId="25" state="visible" r:id="rId25"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_f47_ninchisho" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_自己点検" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_f48_kayoi" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_自己点検" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1649,6 +1650,112 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart21.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>通いの場の実施状況と調査の回答</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'D_f48_kayoi'!B4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'D_f48_kayoi'!$A$5:$A$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_f48_kayoi'!$B$5:$B$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'D_f48_kayoi'!C4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'D_f48_kayoi'!$A$5:$A$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_f48_kayoi'!$C$5:$C$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
@@ -2756,6 +2863,33 @@
 </wsDr>
 </file>
 
+<file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -4574,7 +4708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5549,6 +5683,49 @@
       <c r="I25" s="6" t="inlineStr">
         <is>
           <t>見える化システム J16・J17・J18（厚生労働省「認知症総合支援事業等実施状況調べ」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>図22</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>f48_kayoi</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>計画素案・協議会資料</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>素案 第5章 基本目標1②／協議会資料 第1部4-2</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>通いの場の実施状況と調査の回答</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>縦棒</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>見える化システム F1〜F6及び令和7年度ニーズ調査</t>
         </is>
       </c>
     </row>
@@ -6617,6 +6794,161 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>図22　通いの場の実施状況と調査の回答</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>差し込み先：計画素案・協議会資料　素案 第5章 基本目標1②／協議会資料 第1部4-2　／　種類：縦棒　／　出所：見える化システム F1〜F6及び令和7年度ニーズ調査</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>月1回以上</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>週1回以上</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>平成25</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>平成26</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>平成27</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>平成28</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>平成29</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>平成30</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>令和元</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>令和2</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6681,12 +7013,12 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>21点すべて</t>
+          <t>22点すべて</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>21点</t>
+          <t>22点</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -6708,12 +7040,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>20点すべて</t>
+          <t>21点すべて</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>20点</t>
+          <t>21点</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -6789,12 +7121,12 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>台帳の延べ 23点</t>
+          <t>台帳の延べ 25点</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>成果品の中 23点</t>
+          <t>成果品の中 25点</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -6972,7 +7304,7 @@
         <v>99</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
@@ -7000,7 +7332,7 @@
         <v>50</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
@@ -7216,7 +7548,7 @@
         <v>305</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F14" s="6" t="inlineStr"/>
     </row>
@@ -7441,7 +7773,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>f32_keido／f33_chosa</t>
+          <t>f32_keido／f33_chosa／f48_kayoi</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -7451,7 +7783,7 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>通いの場の参加率・箇所数の推移の図がない</t>
+          <t>令和8年10月1日に通いの場の図を作成。見える化は平成28年度以降0か所である一方、調査では13.8％が年に数回以上参加と回答。この食い違いの解明が要る</t>
         </is>
       </c>
     </row>
@@ -7680,9 +8012,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>済</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -7697,12 +8029,12 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>見える化システム F系列（受領済み）。町の事業実績との食い違いの確認が要る</t>
+          <t>見える化システム F系列（受領済み）。F系列は令和2年度までで、令和3年度以降のデータがない</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>令和8年10月1日に作成（f48_kayoi）。町の事業実績との食い違いの確認は引き続き要る</t>
         </is>
       </c>
     </row>
@@ -7798,7 +8130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -8094,6 +8426,24 @@
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>見える化システム F1〜F6及び令和7年度ニーズ調査</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>受領済み</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>図22</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
